--- a/m1/a1-ecossistema-e-fisica/demonstracao/cotacoes-fornecedores.xlsx
+++ b/m1/a1-ecossistema-e-fisica/demonstracao/cotacoes-fornecedores.xlsx
@@ -442,12 +442,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mapa de cotação · OS 2481 · catálogo institucional 20.000 ex. · exportado em 13/07/2026 14:22</t>
+          <t>Mapa de cotação · OS 2481 · catálogo institucional 20.000 ex. · exportado em 14/07/2026 17:38</t>
         </is>
       </c>
     </row>
@@ -659,11 +659,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Papel offset 90g 66x96</t>
+          <t>Papel couché brilho 150g 66x96</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -672,32 +672,32 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Papelaria Norte</t>
+          <t>Distribuidora Cearapel</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>172.5</v>
+        <v>276.5</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CIF</t>
+          <t>F.O.B.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>28 dias</t>
+          <t>21 dias</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Papel offset 90g 66x96</t>
+          <t>Papel couché fosco 170g 66x96</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -716,34 +716,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Insumos Delta</t>
+          <t>Papelaria Norte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>168,00</t>
+          <t>324,00</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>fob</t>
+          <t>CIF</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>45 dias</t>
+          <t>28 dias</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13-07-26</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Papel offset 90g 66x96</t>
+          <t>Papel couché fosco 170g 66x96</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,119 +762,122 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gráfica Suprimentos SA</t>
-        </is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>309.5</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C.I.F.</t>
+          <t>fob</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>à vista (3% desc.)</t>
+          <t>45 dias</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>13-07-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tinta escala cyan</t>
+          <t>Papel couché fosco 170g 66x96</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>resma</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Papelaria Norte</t>
+          <t>Gráfica Suprimentos SA</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>148</v>
+        <v>318</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CIF</t>
+          <t>C.I.F.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>28 dias</t>
+          <t>à vista (3% desc.)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Papel couché fosco 170g 66x96</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>resma</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>80</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>312,00</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Tinta escala cyan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>18</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Insumos Delta</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>139,00</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>12</v>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>fob</t>
+          <t>F.O.B.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>45 dias</t>
+          <t>21 dias</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13-07-26</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -884,131 +887,170 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tinta escala cyan</t>
+          <t>Papel offset 90g 66x96</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>resma</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gráfica Suprimentos SA</t>
+          <t>Papelaria Norte</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>142.5</v>
+        <v>172.5</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C.I.F.</t>
+          <t>CIF</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>à vista (3% desc.)</t>
+          <t>28 dias</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Papel offset 90g 66x96</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>resma</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>168</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Verniz UV brilho</t>
+          <t>Papel offset 90g 66x96</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>litro</t>
+          <t>resma</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Papelaria Norte</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>96,00</t>
+          <t>Gráfica Suprimentos SA</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CIF</t>
+          <t>C.I.F.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>28 dias</t>
+          <t>à vista (3% desc.)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Verniz UV brilho</t>
+          <t>Papel offset 90g 66x96</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>litro</t>
+          <t>resma</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Insumos Delta</t>
+          <t>Distribuidora Cearapel</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>170</v>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>fob</t>
+          <t>F.O.B.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>45 dias</t>
+          <t>21 dias</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13-07-26</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -1018,189 +1060,1968 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Verniz UV brilho</t>
+          <t>Papel offset 120g 66x96</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>litro</t>
+          <t>resma</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gráfica Suprimentos SA</t>
+          <t>Papelaria Norte</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>93.5</v>
+        <v>198</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C.I.F.</t>
+          <t>CIF</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>à vista (3% desc.)</t>
+          <t>28 dias</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chapa CTP violeta 745x605</t>
+          <t>Papel offset 120g 66x96</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>resma</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Papelaria Norte</t>
+          <t>Insumos Delta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41,50</t>
+          <t>191,00</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CIF</t>
+          <t>fob</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>28 dias</t>
+          <t>45 dias</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>13-07-26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chapa CTP violeta 745x605</t>
+          <t>Papel offset 120g 66x96</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>resma</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Insumos Delta</t>
+          <t>Gráfica Suprimentos SA</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>39.8</v>
+        <v>194.5</v>
       </c>
       <c r="G19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>fob</t>
+          <t>C.I.F.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>45 dias</t>
+          <t>à vista (3% desc.)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13-07-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Papel offset 120g 66x96</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>resma</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>35</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>189</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
         <v>5</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cartão duplex 250g 70x100</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>resma</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>412,00</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cartão duplex 250g 70x100</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>resma</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>60</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>398</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cartão duplex 250g 70x100</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>resma</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>60</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>405</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cartão duplex 250g 70x100</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>resma</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>60</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>401,50</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cartão triplex 300g 70x100</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>resma</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>25</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>487</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cartão triplex 300g 70x100</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>resma</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>469</v>
+      </c>
+      <c r="G26" t="n">
+        <v>12</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cartão triplex 300g 70x100</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>resma</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cartão triplex 300g 70x100</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>resma</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>25</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>474</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tinta escala cyan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>18</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>148</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tinta escala cyan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>18</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>139,00</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tinta escala cyan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>18</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tinta escala cyan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>18</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>141</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tinta escala magenta</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>18</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>151</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tinta escala magenta</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>18</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>142</v>
+      </c>
+      <c r="G35" t="n">
+        <v>12</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Tinta escala magenta</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>18</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>145,00</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>6</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>8</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tinta escala magenta</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tinta escala amarela</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>146</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>9</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tinta escala amarela</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>18</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>137,50</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>12</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>9</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tinta escala amarela</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>18</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>140</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>9</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tinta escala amarela</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>18</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Tinta escala preta</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>30</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>132,00</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>10</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tinta escala preta</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>30</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>124</v>
+      </c>
+      <c r="G43" t="n">
+        <v>12</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>10</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tinta escala preta</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>10</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Tinta escala preta</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>30</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>126,00</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>11</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Verniz UV brilho</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>25</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>96</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Verniz UV brilho</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>25</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>91</v>
+      </c>
+      <c r="G47" t="n">
+        <v>12</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>11</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Verniz UV brilho</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>25</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>93,50</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>11</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Verniz UV brilho</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>25</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>92</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>12</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Verniz acrílico fosco</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>12</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Verniz acrílico fosco</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>84,00</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>12</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>12</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Verniz acrílico fosco</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>12</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Verniz acrílico fosco</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>13</v>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Chapa CTP violeta 745x605</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D54" t="n">
         <v>60</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>41,50</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>13</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Chapa CTP violeta 745x605</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>60</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G55" t="n">
+        <v>12</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>13</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Chapa CTP violeta 745x605</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>60</v>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>Gráfica Suprimentos SA</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F56" t="n">
         <v>40.2</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G56" t="n">
         <v>6</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>C.I.F.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>à vista (3% desc.)</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Frete FOB Insumos Delta: R$ 890,00 (não incluso no valor unitário)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="n">
+        <v>13</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chapa CTP violeta 745x605</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>cx c/ 10</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>60</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>398,00</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>14</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chapa CTP térmica 1030x790</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>45</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>68</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>14</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Chapa CTP térmica 1030x790</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>45</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>12</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>14</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Chapa CTP térmica 1030x790</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>45</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>66,00</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>14</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Chapa CTP térmica 1030x790</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>45</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Frete FOB por conta da Aurora: Insumos Delta R$ 890,00 · Distribuidora Cearapel R$ 1.240,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Produção da OS 2481 entra em máquina em 22/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Cotações válidas por 5 dias corridos a partir da data de envio</t>
         </is>
       </c>
     </row>

--- a/m1/a1-ecossistema-e-fisica/demonstracao/cotacoes-fornecedores.xlsx
+++ b/m1/a1-ecossistema-e-fisica/demonstracao/cotacoes-fornecedores.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>289</v>
+        <v>292.02</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
@@ -591,7 +591,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>271,00</t>
+          <t>271,95</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>283</v>
+        <v>284.49</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>276.5</v>
+        <v>279.67</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -725,7 +725,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>324,00</t>
+          <t>320,07</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>309.5</v>
+        <v>299.9</v>
       </c>
       <c r="G10" t="n">
         <v>12</v>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>318</v>
+        <v>314.13</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>312,00</t>
+          <t>314,53</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>172.5</v>
+        <v>174.3</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>168</v>
+        <v>162.94</v>
       </c>
       <c r="G14" t="n">
         <v>12</v>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>170</v>
+        <v>162.82</v>
       </c>
       <c r="G16" t="n">
         <v>3</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>198</v>
+        <v>198.97</v>
       </c>
       <c r="G17" t="n">
         <v>4</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>191,00</t>
+          <t>183,69</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>194.5</v>
+        <v>191.44</v>
       </c>
       <c r="G19" t="n">
         <v>6</v>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>189</v>
+        <v>186.8</v>
       </c>
       <c r="G20" t="n">
         <v>3</v>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>412,00</t>
+          <t>417,82</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="G22" t="n">
         <v>12</v>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>405</v>
+        <v>397.97</v>
       </c>
       <c r="G23" t="n">
         <v>6</v>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>401,50</t>
+          <t>395,65</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>487</v>
+        <v>493.32</v>
       </c>
       <c r="G25" t="n">
         <v>4</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>469</v>
+        <v>462.58</v>
       </c>
       <c r="G26" t="n">
         <v>12</v>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>474</v>
+        <v>460.41</v>
       </c>
       <c r="G28" t="n">
         <v>3</v>
@@ -1591,16 +1591,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tinta escala cyan</t>
+          <t>Cartão supremo 300g 66x96</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>resma</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>148</v>
+        <v>467.84</v>
       </c>
       <c r="G29" t="n">
         <v>4</v>
@@ -1635,16 +1635,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tinta escala cyan</t>
+          <t>Cartão supremo 300g 66x96</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>resma</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>139,00</t>
+          <t>433,42</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1681,16 +1681,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tinta escala cyan</t>
+          <t>Cartão supremo 300g 66x96</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>resma</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>142.5</v>
+        <v>449.09</v>
       </c>
       <c r="G31" t="n">
         <v>6</v>
@@ -1725,16 +1725,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tinta escala cyan</t>
+          <t>Cartão supremo 300g 66x96</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>resma</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>141</v>
+        <v>446.01</v>
       </c>
       <c r="G32" t="n">
         <v>3</v>
@@ -1760,6 +1760,52 @@
       <c r="J32" t="inlineStr">
         <is>
           <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Papel kraft 80g bobina</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>200</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>9,67</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1815,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tinta escala magenta</t>
+          <t>Papel kraft 80g bobina</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1778,32 +1824,32 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Papelaria Norte</t>
+          <t>Insumos Delta</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>151</v>
+        <v>9.18</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CIF</t>
+          <t>fob</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>28 dias</t>
+          <t>45 dias</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>13-07-26</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1859,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tinta escala magenta</t>
+          <t>Papel kraft 80g bobina</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1822,32 +1868,32 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Insumos Delta</t>
+          <t>Gráfica Suprimentos SA</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>142</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>fob</t>
+          <t>C.I.F.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>45 dias</t>
+          <t>à vista (3% desc.)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>13-07-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1903,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tinta escala magenta</t>
+          <t>Papel kraft 80g bobina</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1866,44 +1912,44 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gráfica Suprimentos SA</t>
+          <t>Distribuidora Cearapel</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>145,00</t>
+          <t>9,32</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C.I.F.</t>
+          <t>F.O.B.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>à vista (3% desc.)</t>
+          <t>21 dias</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tinta escala magenta</t>
+          <t>Tinta escala cyan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1916,28 +1962,28 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Distribuidora Cearapel</t>
+          <t>Papelaria Norte</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>143.5</v>
+        <v>149.46</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>F.O.B.</t>
+          <t>CIF</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>21 dias</t>
+          <t>28 dias</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1993,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tinta escala amarela</t>
+          <t>Tinta escala cyan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1960,28 +2006,28 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Papelaria Norte</t>
+          <t>Insumos Delta</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>146</v>
+        <v>138.56</v>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CIF</t>
+          <t>fob</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>28 dias</t>
+          <t>45 dias</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>13-07-26</t>
         </is>
       </c>
     </row>
@@ -1991,7 +2037,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tinta escala amarela</t>
+          <t>Tinta escala cyan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2004,30 +2050,30 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Insumos Delta</t>
+          <t>Gráfica Suprimentos SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>137,50</t>
+          <t>146,26</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>fob</t>
+          <t>C.I.F.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>45 dias</t>
+          <t>à vista (3% desc.)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>13-07-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2083,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tinta escala amarela</t>
+          <t>Tinta escala cyan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2050,38 +2096,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gráfica Suprimentos SA</t>
+          <t>Distribuidora Cearapel</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>140</v>
+        <v>142.26</v>
       </c>
       <c r="G40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>C.I.F.</t>
+          <t>F.O.B.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>à vista (3% desc.)</t>
+          <t>21 dias</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tinta escala amarela</t>
+          <t>Tinta escala magenta</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2094,25 +2140,28 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Distribuidora Cearapel</t>
-        </is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>152.91</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>F.O.B.</t>
+          <t>CIF</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>21 dias</t>
+          <t>28 dias</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2171,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tinta escala preta</t>
+          <t>Tinta escala magenta</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2131,34 +2180,34 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Papelaria Norte</t>
+          <t>Insumos Delta</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>132,00</t>
+          <t>139,59</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CIF</t>
+          <t>fob</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>28 dias</t>
+          <t>45 dias</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>13-07-26</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2217,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tinta escala preta</t>
+          <t>Tinta escala magenta</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2177,32 +2226,32 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Insumos Delta</t>
+          <t>Gráfica Suprimentos SA</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>124</v>
+        <v>147.7</v>
       </c>
       <c r="G43" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>fob</t>
+          <t>C.I.F.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>45 dias</t>
+          <t>à vista (3% desc.)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>13-07-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2261,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tinta escala preta</t>
+          <t>Tinta escala magenta</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2221,42 +2270,42 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gráfica Suprimentos SA</t>
+          <t>Distribuidora Cearapel</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>127.5</v>
+        <v>142.76</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>C.I.F.</t>
+          <t>F.O.B.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>à vista (3% desc.)</t>
+          <t>21 dias</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tinta escala preta</t>
+          <t>Tinta escala amarela</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2265,34 +2314,34 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Distribuidora Cearapel</t>
+          <t>Papelaria Norte</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>126,00</t>
+          <t>147,95</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>F.O.B.</t>
+          <t>CIF</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>21 dias</t>
+          <t>28 dias</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2302,41 +2351,41 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Verniz UV brilho</t>
+          <t>Tinta escala amarela</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>litro</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Papelaria Norte</t>
+          <t>Insumos Delta</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>96</v>
+        <v>137.92</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CIF</t>
+          <t>fob</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>28 dias</t>
+          <t>45 dias</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>13-07-26</t>
         </is>
       </c>
     </row>
@@ -2346,41 +2395,41 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Verniz UV brilho</t>
+          <t>Tinta escala amarela</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>litro</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Insumos Delta</t>
+          <t>Gráfica Suprimentos SA</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>91</v>
+        <v>143.66</v>
       </c>
       <c r="G47" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>fob</t>
+          <t>C.I.F.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>45 dias</t>
+          <t>à vista (3% desc.)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>13-07-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2390,87 +2439,82 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Verniz UV brilho</t>
+          <t>Tinta escala amarela</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>litro</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gráfica Suprimentos SA</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>93,50</t>
+          <t>Distribuidora Cearapel</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>C.I.F.</t>
+          <t>F.O.B.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>à vista (3% desc.)</t>
+          <t>21 dias</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Verniz UV brilho</t>
+          <t>Tinta escala preta</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>litro</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Distribuidora Cearapel</t>
+          <t>Papelaria Norte</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>92</v>
+        <v>131.9</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>F.O.B.</t>
+          <t>CIF</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>21 dias</t>
+          <t>28 dias</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2480,41 +2524,41 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Verniz acrílico fosco</t>
+          <t>Tinta escala preta</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>litro</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Papelaria Norte</t>
+          <t>Insumos Delta</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>88.5</v>
+        <v>122.33</v>
       </c>
       <c r="G50" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CIF</t>
+          <t>fob</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>28 dias</t>
+          <t>45 dias</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>13-07-26</t>
         </is>
       </c>
     </row>
@@ -2524,43 +2568,43 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Verniz acrílico fosco</t>
+          <t>Tinta escala preta</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>litro</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Insumos Delta</t>
+          <t>Gráfica Suprimentos SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>84,00</t>
+          <t>128,69</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>fob</t>
+          <t>C.I.F.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>45 dias</t>
+          <t>à vista (3% desc.)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>13-07-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2570,82 +2614,85 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Verniz acrílico fosco</t>
+          <t>Tinta escala preta</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>litro</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gráfica Suprimentos SA</t>
-        </is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>127.06</v>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>C.I.F.</t>
+          <t>F.O.B.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>à vista (3% desc.)</t>
+          <t>21 dias</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
+        <v>13</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tinta Pantone 485C</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>12</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Verniz acrílico fosco</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>litro</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>15</v>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Distribuidora Cearapel</t>
+          <t>Papelaria Norte</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>85.5</v>
+        <v>215.51</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>F.O.B.</t>
+          <t>CIF</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>21 dias</t>
+          <t>28 dias</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
     </row>
@@ -2655,43 +2702,43 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chapa CTP violeta 745x605</t>
+          <t>Tinta Pantone 485C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Papelaria Norte</t>
+          <t>Insumos Delta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>41,50</t>
+          <t>199,68</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CIF</t>
+          <t>fob</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>28 dias</t>
+          <t>45 dias</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>13-07-26</t>
         </is>
       </c>
     </row>
@@ -2701,41 +2748,41 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chapa CTP violeta 745x605</t>
+          <t>Tinta Pantone 485C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Insumos Delta</t>
+          <t>Gráfica Suprimentos SA</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>39.8</v>
+        <v>206.86</v>
       </c>
       <c r="G55" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>fob</t>
+          <t>C.I.F.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>45 dias</t>
+          <t>à vista (3% desc.)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>13-07-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -2745,85 +2792,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chapa CTP violeta 745x605</t>
+          <t>Tinta Pantone 485C</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gráfica Suprimentos SA</t>
+          <t>Distribuidora Cearapel</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>40.2</v>
+        <v>202.93</v>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>C.I.F.</t>
+          <t>F.O.B.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>à vista (3% desc.)</t>
+          <t>21 dias</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>13</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Chapa CTP violeta 745x605</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>cx c/ 10</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>60</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Distribuidora Cearapel</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>398,00</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>F.O.B.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>21 dias</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
@@ -2835,16 +2836,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chapa CTP térmica 1030x790</t>
+          <t>Tinta Pantone 072C</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2852,7 +2853,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>68</v>
+        <v>225.18</v>
       </c>
       <c r="G58" t="n">
         <v>4</v>
@@ -2879,16 +2880,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chapa CTP térmica 1030x790</t>
+          <t>Tinta Pantone 072C</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2896,7 +2897,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>64.5</v>
+        <v>210.91</v>
       </c>
       <c r="G59" t="n">
         <v>12</v>
@@ -2923,16 +2924,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chapa CTP térmica 1030x790</t>
+          <t>Tinta Pantone 072C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2941,7 +2942,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>66,00</t>
+          <t>222,98</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2969,21 +2970,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chapa CTP térmica 1030x790</t>
+          <t>Tinta Pantone 072C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Distribuidora Cearapel</t>
         </is>
+      </c>
+      <c r="F61" t="n">
+        <v>217.58</v>
       </c>
       <c r="G61" t="n">
         <v>3</v>
@@ -3004,22 +3008,2147 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>15</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Verniz UV brilho</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>25</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="G62" t="n">
+        <v>4</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" t="n">
+        <v>15</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Verniz UV brilho</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>25</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>88,95</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>12</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>15</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Verniz UV brilho</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>25</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>94.33</v>
+      </c>
+      <c r="G64" t="n">
+        <v>6</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>15</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Verniz UV brilho</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>25</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>92.28</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>16</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Verniz acrílico fosco</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>15</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>89,33</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>4</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>16</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Verniz acrílico fosco</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>15</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="G67" t="n">
+        <v>12</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>16</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Verniz acrílico fosco</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>15</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>6</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>16</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Verniz acrílico fosco</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>15</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>85,01</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>3</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>17</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Verniz de sobreimpressão</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>20</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>79.14</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>17</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Verniz de sobreimpressão</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>20</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="G71" t="n">
+        <v>12</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>17</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Verniz de sobreimpressão</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>20</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>76,96</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>6</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>17</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Verniz de sobreimpressão</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>20</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>74.92</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>18</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Chapa CTP violeta 745x605</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>60</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>18</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chapa CTP violeta 745x605</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>60</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>38,56</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>18</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Chapa CTP violeta 745x605</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>60</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>40.69</v>
+      </c>
+      <c r="G76" t="n">
+        <v>6</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>18</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Chapa CTP violeta 745x605</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>cx c/ 10</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>60</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>392.3</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>19</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Chapa CTP térmica 1030x790</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>45</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>67,76</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>19</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Chapa CTP térmica 1030x790</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>45</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>63.36</v>
+      </c>
+      <c r="G79" t="n">
+        <v>12</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>19</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Chapa CTP térmica 1030x790</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>45</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>65.77</v>
+      </c>
+      <c r="G80" t="n">
+        <v>6</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>19</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Chapa CTP térmica 1030x790</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>45</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>3</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>20</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Blanqueta offset 1030x790</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>8</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>740.99</v>
+      </c>
+      <c r="G82" t="n">
+        <v>4</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>20</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Blanqueta offset 1030x790</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>8</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>704.0599999999999</v>
+      </c>
+      <c r="G83" t="n">
+        <v>12</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>20</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Blanqueta offset 1030x790</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>8</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>6</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>20</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Blanqueta offset 1030x790</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>8</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>705.42</v>
+      </c>
+      <c r="G85" t="n">
+        <v>3</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>21</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Filme BOPP laminação brilho</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>21</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Filme BOPP laminação brilho</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>12</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>21</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Filme BOPP laminação brilho</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G88" t="n">
+        <v>6</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>21</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Filme BOPP laminação brilho</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G89" t="n">
+        <v>3</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>22</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Filme BOPP laminação fosco</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>4</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>22</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Filme BOPP laminação fosco</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G91" t="n">
+        <v>12</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>22</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Filme BOPP laminação fosco</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>22</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Filme BOPP laminação fosco</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2,03</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>3</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>23</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Cola hot melt</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>40</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G94" t="n">
+        <v>4</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>23</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Cola hot melt</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>40</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="G95" t="n">
+        <v>12</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>23</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Cola hot melt</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>40</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>27,23</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>6</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>23</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Cola hot melt</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>40</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>3</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>24</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Solvente de limpeza</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>60</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="G98" t="n">
+        <v>4</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>24</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Solvente de limpeza</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>60</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>17,95</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>12</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>24</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Solvente de limpeza</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>60</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="G100" t="n">
+        <v>6</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>24</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Solvente de limpeza</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>60</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="G101" t="n">
+        <v>3</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>25</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Wire-o preto 3/4</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>500</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>3,40</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>4</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>25</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Wire-o preto 3/4</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>500</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="G103" t="n">
+        <v>12</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>25</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Wire-o preto 3/4</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>500</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>6</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>25</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Wire-o preto 3/4</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>500</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>3,22</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>3</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>26</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Fita dupla face 12mm</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>rolo</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>60</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Papelaria Norte</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="G106" t="n">
+        <v>4</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>CIF</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>28 dias</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>26</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Fita dupla face 12mm</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>rolo</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>60</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Insumos Delta</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="G107" t="n">
+        <v>12</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>fob</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>45 dias</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>13-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>26</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Fita dupla face 12mm</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>rolo</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>60</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Gráfica Suprimentos SA</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>22,52</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>6</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>C.I.F.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>à vista (3% desc.)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>26</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Fita dupla face 12mm</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>rolo</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>60</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Distribuidora Cearapel</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>F.O.B.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>21 dias</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>Frete FOB por conta da Aurora: Insumos Delta R$ 890,00 · Distribuidora Cearapel R$ 1.240,00</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>Produção da OS 2481 entra em máquina em 22/07/2026</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>Cotações válidas por 5 dias corridos a partir da data de envio</t>
         </is>
